--- a/site/exports/cqu-architecture-urban-planning.xlsx
+++ b/site/exports/cqu-architecture-urban-planning.xlsx
@@ -453,7 +453,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="26.6" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -482,7 +482,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>核对日期</t>
+          <t>已记录来源检索日期</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -549,12 +549,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录；部分公开职业事实，教育、师承和人事在岗仍有缺项；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：建筑设计(1)+(2)；主讲；教学／课程开设时间：时间未披露；报道明确主讲课程；未声称2026仍授课。；来源ID：cqu-chenke-teaching-2021；https://news.cqu.edu.cn/archives/news2/content/2021/04/01/eeab4ef47653f3eca46265fa0c4a0a4d4a1eb0e4.html；官方旧文完整缓存正文已读；原地址直连404，仅支持历史事实，关闭失效来源导航。；official_cached_body_read_direct_404 | 泛设计思维；主讲；教学／课程开设时间：时间未披露；系列讲座首场、18日晚由本人主讲；不是学期课程或长期任课。；来源教学时期：2025-09-18；来源ID：cqu-chenke-lecture-2025；https://news.cqu.edu.cn/archives/news2/content/2025/09/19/6bab3d43eb9c2f730772541ee4d983ff5aced5f3.html；官方旧文完整缓存正文已读；原地址直连404，仅支持历史事实，关闭失效来源导航。；official_cached_body_read_direct_404</t>
+          <t>分批核实资料，不是完整名录；部分公开职业事实，教育、师承和人事在岗仍有缺项；公开教学事实（非本人求学学历；教学／课程开设时间不是入学、授位或任职起点；不计入教育、任职、论文、导师统计及师承图）：建筑设计(1)+(2)；主讲；教学／课程开设时间：时间未披露；报道明确主讲课程；未声称2026仍授课。；来源ID：cqu-chenke-teaching-2021；https://news.cqu.edu.cn/archives/news2/content/2021/04/01/eeab4ef47653f3eca46265fa0c4a0a4d4a1eb0e4.html；官方旧文完整缓存正文已读；原地址直连404，仅支持历史事实，关闭失效来源导航。；official_cached_body_read_direct_404 | 泛设计思维；主讲；教学／课程开设时间：时间未披露；系列讲座首场、18日晚由本人主讲；不是学期课程或长期任课。；来源教学时期：2025-09-18；来源ID：cqu-chenke-lecture-2025；https://news.cqu.edu.cn/archives/news2/content/2025/09/19/6bab3d43eb9c2f730772541ee4d983ff5aced5f3.html；官方旧文完整缓存正文已读；原地址直连404，仅支持历史事实，关闭失效来源导航。；official_cached_body_read_direct_404；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -602,12 +602,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
